--- a/Assets/test260903/chapter0205.xlsx
+++ b/Assets/test260903/chapter0205.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="314" documentId="11_8E1AFE78FBD34A042E83A027A8BF20349734C0B7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FF6ED99-642B-464F-9370-6D1E9BDBACA9}"/>
+  <bookViews>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="chapter0205" sheetId="1" r:id="rId4"/>
+    <sheet name="chapter0205" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="1wnk63aERf7/uTyT6okFjiq/Ayajw31Os+0y4XC6imY="/>
@@ -16,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="141">
   <si>
     <t>Command</t>
   </si>
@@ -66,9 +75,6 @@
     <t>WaitInput</t>
   </si>
   <si>
-    <t>BgOff</t>
-  </si>
-  <si>
     <t>Chapter2-5です</t>
   </si>
   <si>
@@ -76,27 +82,616 @@
   </si>
   <si>
     <t>*chapter0206_Start</t>
+  </si>
+  <si>
+    <t>少年は戦場へ放り込まれた</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>背景：黒</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>FadeIn</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>black</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Se</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>銃撃戦（連射）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>血肉が飛び交い、硝煙の香りが満ちる。
+あちこちで怒声と罵声が上がる</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>しかし、少年は確かに聞いた</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>女の笑い声を。
+獲物を前にした肉食獣の高笑いを</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そして、静寂が訪れた。
+女の微笑みだけを残して</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>StopSe</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ふぅ……久々に高ぶった。
+普通に「ありがとう」って言いたい</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>鈴野美鈴</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>喜び</t>
+    <rPh sb="0" eb="1">
+      <t>ヨロコ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>背景：会社のエントランス（戦闘後）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>全力で、100パーで戦えたわ。
+ありがとね</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>んぐっ……ぐっ……挨拶はいい、早く、
+撃て……喉が裂けてるんだ、こっちは</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>白蛇の男</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>負傷</t>
+    <rPh sb="0" eb="2">
+      <t>フショウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>美鈴さんは暴れた。
+戦ったんじゃない。暴れたんだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>主人公</t>
+    <rPh sb="0" eb="3">
+      <t>シュジンコウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>戦略もクソもない。
+その場その場の最適解に飛びついた</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そして、勝ってしまった。
+美鈴さんは、今……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ロケットランチャーを撃ち込んできた、
+あの白蛇の男に銃を突き付けている</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>こんな真似して……
+助かる……はずもない……ぞ……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>お前は、俺たちの組織を……
+白蛇全体を敵に……回し……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>だから？
+相手が誰だろうが、ムカついたら殴る</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>怒り</t>
+    <rPh sb="0" eb="1">
+      <t>イカ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そういう性格だから、
+こういう仕事をしてるんじゃないの？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……ぐっ……がっ、かも……なっ……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>次に生まれてくるときは、
+ちゃんと仕事を選んで受けるように</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>通常</t>
+    <rPh sb="0" eb="2">
+      <t>ツウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……そう……する……か……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>じゃあね</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ぐっ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>銃声（単発）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>&lt;Off&gt;</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>さて、こっちは片付いた。
+次は……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>お前の叔父さんだな、エロガキ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>美鈴さんが銃口を向けた。
+その先には……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>銃を構える</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>叔父がいた。
+震えて、亀のように丸まっている</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>叔父</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>怯え</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>しかし、眼だけは違った。
+ギラギラと輝き、今にも飛び出しそうだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ききき、貴様が！　貴様が悪い！
+何で生きてるんだ、この野郎！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>逆上</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>殺せって命令したぞ！
+金も払ったし、たくさん払ったんだぞ！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……そりゃ残念。
+まぁ、相手が悪かったよね</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>こいつの護衛、無敵のアタシだから。
+アタシじゃなけりゃ成功してたと思うよ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ねーエロガキ、もう撃っていい？
+こいつ、アタシが一番嫌いなヤツっぽい</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>し、白蛇ー！　白蛇はどうした！
+何をやってるんだ、連中はー！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>あああーー！　何でだー！　
+詐欺、詐欺だ！　騙されたー！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>おっ、師匠から着信だ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>電話</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>もしもし？
+師匠、そっちはどう？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>話し合いなら、もう終わったわい</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>師匠</t>
+    <rPh sb="0" eb="2">
+      <t>シショウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>仁義を欠いた幹部連中は、
+まとめてシベリアへ行くことになった</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>組織体制を一新すると誓ってもらった。
+その子どもの仕事も撤回させたぞ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>にしても、本当に喧嘩ができんのう。
+体もダルダルで、脂肪の塊じゃ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>白蛇はそもそも、数千年の歴史を持つ、
+大陸最強の武侠集団であり……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>あっ、その話になると
+師匠っていつも長いから！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>切るねー！　ありがとねー！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……ゴホン。というわけで～、
+白蛇は、この件から手を引いた</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……で、エロガキさ。
+このおっさんは、どうする？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>お前が決めていいよ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ただし、
+ひとつだけアドバイスしておく</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>血のつながりなんて、忘れた方がいい。
+こいつはお前を殺そうとした</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>その事実を大事にした方がいいと思うよ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>黙ってろクソ女ー！
+お前が、お前がいなければ！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そこのガキも、安らかに死ねたんだぞ！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>は？　はぁ？　はぁぁーーーー？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ああ、そうだ、その通りだ。
+ガキめ、お前が全部悪いんだ、そうだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>お前が生まれてきたのが悪い。
+お前がいなけりゃ、そもそも良かった</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>教えてやるよ、お父さんだ！
+お前の父が命令したんだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>お前を殺せってな。
+はは、酷いもんだよなぁ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>今の妻の圧が凄いらしいぜ。
+それで、邪魔だから死ねってさ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>お前、生きててもいいことないぞぉ？
+だから、死んだ方がよかったぞぉ？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>はははっ、ははぁ……はぁーーー？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>何で俺が殺されかけてんだーー！？
+死にたくねぇー！　助けてくれー！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……叔父は、僕の足首にすがる</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>「狂った」と判断するべきだろう。
+人は狂うとこうなるのか</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……おい、エロガキ。
+どうするか、早く決めよう</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>この街の警察は、基本的に、
+黒社会の揉め事に触れないけど……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そろそろ来るよ。
+あと、そいつ……お前の叔父さんさぁ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>たぶん、もうダメだよ。
+思考回路がショートしてる</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……その通りだ。叔父はもう終わった</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>しかし……
+やはり両親が、僕を殺そうとしたのか</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>おーい</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>僕が両親に内緒で貯めた現金と、
+信頼できる会社役員陣のリストはある</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>僕は……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>おーいってば</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Selection</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0205-5-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0205-1-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>行こう</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>行くって？　どこに？
+つーか、こいつはどうすんの？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0205-2-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>行くのは、東京だ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>は？　なんで？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0205-3-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>僕は、両親を殴る</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>おおっ、何で？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0205-4-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>殺されかけて、ムカついたから</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……はははは！　上等っ♪</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そうだよエロガキ、
+そういう感じが大事なんだって</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>あなたを護衛として雇い続ける</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>うん、了解</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>つーかさ、
+勝手について行きたかったくらいだから</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0205-6-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>どうしてです？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そもそも、お前の両親が
+「エロガキ殺し」を言い出したんだろ？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>で、アタシにケンカを売ってきた。
+だったら、アタシも殴る権利がある</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0205-7-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>なるほど</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>でしょっ！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>よっしゃ！
+そうと決まれば空港だ！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0205-8-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>了解！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>FadeOut</t>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -104,49 +699,71 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -336,28 +953,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L1068"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="11.5"/>
-    <col customWidth="1" min="2" max="2" width="14.0"/>
-    <col customWidth="1" min="3" max="7" width="5.13"/>
-    <col customWidth="1" min="8" max="8" width="8.63"/>
-    <col customWidth="1" min="9" max="9" width="37.75"/>
-    <col customWidth="1" min="10" max="10" width="8.25"/>
-    <col customWidth="1" min="11" max="11" width="6.0"/>
-    <col customWidth="1" min="12" max="12" width="11.38"/>
-    <col customWidth="1" min="13" max="26" width="8.0"/>
+    <col min="1" max="1" width="11.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="7" width="5.109375" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" customWidth="1"/>
+    <col min="9" max="9" width="37.77734375" customWidth="1"/>
+    <col min="10" max="10" width="8.21875" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="11.33203125" customWidth="1"/>
+    <col min="13" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" spans="1:12" ht="13.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -395,686 +1012,1379 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="1"/>
       <c r="H2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="6">
-        <v>3.0</v>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4">
+        <v>3</v>
       </c>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" ht="13.5" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
+    <row r="5" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" ht="13.5" customHeight="1">
+    <row r="6" spans="1:12" ht="13.5" customHeight="1">
       <c r="B6" s="1"/>
       <c r="H6" s="1"/>
-      <c r="I6" s="3" t="s">
-        <v>17</v>
+      <c r="I6" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>19</v>
+    <row r="7" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-    </row>
-    <row r="8" ht="13.5" customHeight="1">
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:12" ht="13.2" customHeight="1">
+      <c r="A8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-    </row>
-    <row r="9" ht="13.5" customHeight="1">
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:12" ht="13.2" customHeight="1">
+      <c r="A9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1"/>
       <c r="I9" s="1"/>
-    </row>
-    <row r="10" ht="13.5" customHeight="1">
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" ht="13.5" customHeight="1">
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" ht="13.5" customHeight="1">
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-    </row>
-    <row r="13" ht="13.5" customHeight="1">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-    </row>
-    <row r="14" ht="13.5" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-    </row>
-    <row r="15" ht="13.5" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-    </row>
-    <row r="16" ht="13.5" customHeight="1">
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-    </row>
-    <row r="17" ht="13.5" customHeight="1">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="I17" s="1"/>
-    </row>
-    <row r="18" ht="13.5" customHeight="1">
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:12" ht="13.5" customHeight="1">
+      <c r="H10" s="1"/>
+      <c r="I10" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="28.2" customHeight="1">
+      <c r="I11" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="13.5" customHeight="1">
+      <c r="I12" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="30" customHeight="1">
+      <c r="I13" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="30" customHeight="1">
+      <c r="A14" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="8"/>
+    </row>
+    <row r="15" spans="1:12" ht="30.6" customHeight="1">
+      <c r="I15" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="30.6" customHeight="1">
+      <c r="A16" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I16" s="8"/>
+    </row>
+    <row r="17" spans="1:10" ht="30" customHeight="1">
+      <c r="B17" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:10" ht="30" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" ht="13.5" customHeight="1">
+      <c r="B18" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="I18" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:10" ht="28.2" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="I19" s="1"/>
-    </row>
-    <row r="20" ht="13.5" customHeight="1">
+      <c r="B19" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" spans="1:10" ht="30" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" ht="13.5" customHeight="1">
-      <c r="B21" s="1"/>
+      <c r="B20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="I20" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B21" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="C21" s="1"/>
-      <c r="I21" s="1"/>
-    </row>
-    <row r="22" ht="13.5" customHeight="1">
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="I22" s="1"/>
-    </row>
-    <row r="23" ht="13.5" customHeight="1">
+      <c r="I21" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J21" s="1"/>
+    </row>
+    <row r="22" spans="1:10" ht="30.6" customHeight="1">
+      <c r="A22" s="1"/>
+      <c r="B22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="27.6" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-    </row>
-    <row r="24" ht="13.5" customHeight="1">
+      <c r="B23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="28.8" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-    </row>
-    <row r="25" ht="13.5" customHeight="1">
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="I25" s="1"/>
-    </row>
-    <row r="26" ht="13.5" customHeight="1">
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="I26" s="1"/>
-    </row>
-    <row r="27" ht="13.5" customHeight="1">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-    </row>
-    <row r="28" ht="13.5" customHeight="1">
+      <c r="B24" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="30" customHeight="1">
+      <c r="A25" s="1"/>
+      <c r="B25" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H25" s="1"/>
+      <c r="I25" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="30" customHeight="1">
+      <c r="B26" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B27" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="13.5" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="I28" s="1"/>
+      <c r="B28" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="J28" s="1"/>
     </row>
-    <row r="29" ht="13.5" customHeight="1">
-      <c r="I29" s="1"/>
-    </row>
-    <row r="30" ht="13.5" customHeight="1">
-      <c r="I30" s="1"/>
-    </row>
-    <row r="31" ht="13.5" customHeight="1">
-      <c r="I31" s="1"/>
-    </row>
-    <row r="32" ht="13.5" customHeight="1">
-      <c r="I32" s="1"/>
-    </row>
-    <row r="33" ht="13.5" customHeight="1">
-      <c r="I33" s="1"/>
-    </row>
-    <row r="34" ht="13.5" customHeight="1">
+    <row r="29" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A29" s="1"/>
+      <c r="B29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B30" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B31" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A32" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="6"/>
+      <c r="I32" s="8"/>
+    </row>
+    <row r="33" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A33" s="1"/>
+      <c r="B33" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A34" s="1"/>
+      <c r="B34" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>55</v>
+      </c>
       <c r="I34" s="1"/>
-    </row>
-    <row r="35" ht="13.5" customHeight="1">
-      <c r="I35" s="1"/>
-    </row>
-    <row r="36" ht="13.5" customHeight="1">
-      <c r="I36" s="1"/>
-    </row>
-    <row r="37" ht="13.5" customHeight="1">
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="I37" s="1"/>
-    </row>
-    <row r="38" ht="13.5" customHeight="1">
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="I38" s="1"/>
-    </row>
-    <row r="39" ht="13.5" customHeight="1">
-      <c r="I39" s="1"/>
-    </row>
-    <row r="40" ht="13.5" customHeight="1">
-      <c r="I40" s="1"/>
-    </row>
-    <row r="41" ht="13.5" customHeight="1">
-      <c r="I41" s="1"/>
-    </row>
-    <row r="42" ht="13.5" customHeight="1">
-      <c r="I42" s="1"/>
-    </row>
-    <row r="43" ht="13.5" customHeight="1">
-      <c r="I43" s="1"/>
-    </row>
-    <row r="44" ht="13.5" customHeight="1">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="I44" s="1"/>
-    </row>
-    <row r="45" ht="13.5" customHeight="1">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="I45" s="1"/>
-    </row>
-    <row r="46" ht="13.5" customHeight="1">
-      <c r="A46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-    </row>
-    <row r="47" ht="13.5" customHeight="1">
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="I47" s="1"/>
-    </row>
-    <row r="48" ht="13.5" customHeight="1">
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-    </row>
-    <row r="49" ht="13.5" customHeight="1">
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-    </row>
-    <row r="50" ht="13.5" customHeight="1">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-    </row>
-    <row r="51" ht="13.5" customHeight="1">
-      <c r="A51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-    </row>
-    <row r="52" ht="13.5" customHeight="1">
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="I52" s="1"/>
-    </row>
-    <row r="53" ht="13.5" customHeight="1">
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="I53" s="1"/>
-    </row>
-    <row r="54" ht="13.5" customHeight="1">
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B35" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B36" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A37" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C37" s="6"/>
+      <c r="I37" s="8"/>
+    </row>
+    <row r="38" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B38" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B39" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I39" s="8"/>
+    </row>
+    <row r="40" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B40" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B41" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B42" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="30" customHeight="1">
+      <c r="B43" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B44" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B45" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B46" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="30" customHeight="1">
+      <c r="B47" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B48" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A49" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C49" s="5"/>
+      <c r="I49" s="8"/>
+    </row>
+    <row r="50" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B50" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B51" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B52" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A53" s="1"/>
+      <c r="B53" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="31.8" customHeight="1">
       <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-      <c r="I54" s="1"/>
-    </row>
-    <row r="55" ht="13.5" customHeight="1">
+      <c r="B54" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="28.8" customHeight="1">
       <c r="A55" s="1"/>
-      <c r="I55" s="1"/>
-    </row>
-    <row r="56" ht="13.5" customHeight="1">
-      <c r="I56" s="1"/>
-    </row>
-    <row r="57" ht="13.5" customHeight="1">
-      <c r="I57" s="1"/>
-    </row>
-    <row r="58" ht="13.5" customHeight="1">
-      <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
-      <c r="I58" s="1"/>
-    </row>
-    <row r="59" ht="13.5" customHeight="1">
+      <c r="B55" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="J55" s="1"/>
+    </row>
+    <row r="56" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B56" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B57" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="J57" s="1"/>
+    </row>
+    <row r="58" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B58" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="J58" s="1"/>
+    </row>
+    <row r="59" spans="1:10" ht="30" customHeight="1">
       <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
-      <c r="I59" s="1"/>
-    </row>
-    <row r="60" ht="13.5" customHeight="1">
-      <c r="B60" s="1"/>
-      <c r="C60" s="1"/>
-      <c r="I60" s="1"/>
-    </row>
-    <row r="61" ht="13.5" customHeight="1">
-      <c r="B61" s="1"/>
-      <c r="C61" s="1"/>
-      <c r="I61" s="1"/>
-    </row>
-    <row r="62" ht="13.5" customHeight="1">
-      <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
-      <c r="I62" s="1"/>
-    </row>
-    <row r="63" ht="13.5" customHeight="1">
-      <c r="B63" s="1"/>
-      <c r="C63" s="1"/>
-      <c r="I63" s="1"/>
-    </row>
-    <row r="64" ht="13.5" customHeight="1">
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="J59" s="1"/>
+    </row>
+    <row r="60" spans="1:10" ht="30" customHeight="1">
+      <c r="A60" s="1"/>
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="J60" s="1"/>
+    </row>
+    <row r="61" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B62" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A63" s="1"/>
+      <c r="B63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="13.5" customHeight="1">
       <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
-      <c r="I64" s="1"/>
-    </row>
-    <row r="65" ht="13.5" customHeight="1">
-      <c r="A65" s="1"/>
-      <c r="B65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-    </row>
-    <row r="66" ht="13.5" customHeight="1">
-      <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-      <c r="I66" s="1"/>
-    </row>
-    <row r="67" ht="13.5" customHeight="1">
-      <c r="B67" s="1"/>
-      <c r="C67" s="1"/>
-      <c r="I67" s="1"/>
-    </row>
-    <row r="68" ht="13.5" customHeight="1">
+      <c r="B64" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B65" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I65" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B66" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I66" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A67" s="1"/>
+      <c r="B67" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I67" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="30.6" customHeight="1">
       <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
-      <c r="I68" s="1"/>
-    </row>
-    <row r="69" ht="13.5" customHeight="1">
-      <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-    </row>
-    <row r="70" ht="13.5" customHeight="1">
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="I70" s="1"/>
-    </row>
-    <row r="71" ht="13.5" customHeight="1">
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="I71" s="1"/>
-    </row>
-    <row r="72" ht="13.5" customHeight="1">
-      <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-      <c r="I72" s="1"/>
-    </row>
-    <row r="73" ht="13.5" customHeight="1">
-      <c r="B73" s="1"/>
-      <c r="C73" s="1"/>
-      <c r="I73" s="1"/>
-    </row>
-    <row r="74" ht="13.5" customHeight="1">
-      <c r="B74" s="1"/>
-      <c r="C74" s="1"/>
-      <c r="I74" s="1"/>
-    </row>
-    <row r="75" ht="13.5" customHeight="1">
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-      <c r="I75" s="1"/>
-    </row>
-    <row r="76" ht="13.5" customHeight="1">
-      <c r="B76" s="1"/>
+      <c r="B68" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I68" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B69" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I69" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B70" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B71" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I71" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B72" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I72" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="30" customHeight="1">
+      <c r="A73" s="1"/>
+      <c r="B73" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I73" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A74" s="1"/>
+      <c r="B74" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H74" s="1"/>
+      <c r="I74" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="30" customHeight="1">
+      <c r="B75" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I75" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B76" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="C76" s="1"/>
-      <c r="I76" s="1"/>
-    </row>
-    <row r="77" ht="13.5" customHeight="1">
-      <c r="B77" s="1"/>
-      <c r="C77" s="1"/>
-      <c r="I77" s="1"/>
-    </row>
-    <row r="78" ht="13.5" customHeight="1">
-      <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
-    </row>
-    <row r="79" ht="13.5" customHeight="1">
-      <c r="I79" s="1"/>
-    </row>
-    <row r="80" ht="13.5" customHeight="1">
-      <c r="I80" s="1"/>
-    </row>
-    <row r="81" ht="13.5" customHeight="1">
-      <c r="I81" s="1"/>
-    </row>
-    <row r="82" ht="13.5" customHeight="1">
-      <c r="A82" s="1"/>
-      <c r="B82" s="1"/>
-      <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
-    </row>
-    <row r="83" ht="13.5" customHeight="1">
-      <c r="A83" s="1"/>
-      <c r="B83" s="1"/>
-      <c r="I83" s="1"/>
-      <c r="J83" s="1"/>
-    </row>
-    <row r="84" ht="13.5" customHeight="1">
-      <c r="A84" s="1"/>
-    </row>
-    <row r="85" ht="13.5" customHeight="1">
-      <c r="B85" s="1"/>
+      <c r="I76" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="31.8" customHeight="1">
+      <c r="A77" s="1"/>
+      <c r="B77" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I77" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="31.8" customHeight="1">
+      <c r="A78" s="1"/>
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H78" s="1"/>
+      <c r="I78" s="8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I79" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I80" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="30" customHeight="1">
+      <c r="B81" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I81" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B82" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C82" s="1"/>
+      <c r="I82" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="30" customHeight="1">
+      <c r="B83" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C83" s="1"/>
+      <c r="I83" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B84" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I84" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B85" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="C85" s="1"/>
-      <c r="I85" s="1"/>
-    </row>
-    <row r="86" ht="13.5" customHeight="1">
-      <c r="B86" s="1"/>
+      <c r="I85" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B86" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="C86" s="1"/>
-      <c r="I86" s="1"/>
-    </row>
-    <row r="87" ht="13.5" customHeight="1">
-      <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
-      <c r="I87" s="1"/>
-    </row>
-    <row r="88" ht="13.5" customHeight="1">
-      <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
-      <c r="I88" s="1"/>
-    </row>
-    <row r="89" ht="13.5" customHeight="1">
-      <c r="A89" s="1"/>
-      <c r="B89" s="1"/>
-    </row>
-    <row r="90" ht="13.5" customHeight="1">
-      <c r="A90" s="1"/>
-    </row>
-    <row r="91" ht="13.5" customHeight="1">
-      <c r="B91" s="1"/>
-      <c r="C91" s="1"/>
-      <c r="I91" s="1"/>
-    </row>
-    <row r="92" ht="13.5" customHeight="1">
+      <c r="I86" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B87" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I87" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="J87" s="1"/>
+    </row>
+    <row r="88" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A88" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I88" s="8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A89" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I89" s="1"/>
+    </row>
+    <row r="90" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B90" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I90" s="8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A91" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I91" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="J91" s="1"/>
+    </row>
+    <row r="92" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A92" s="1" t="s">
+        <v>117</v>
+      </c>
       <c r="B92" s="1"/>
-      <c r="C92" s="1"/>
       <c r="I92" s="1"/>
-    </row>
-    <row r="93" ht="13.5" customHeight="1">
-      <c r="B93" s="1"/>
-      <c r="C93" s="1"/>
-      <c r="I93" s="1"/>
-    </row>
-    <row r="94" ht="13.5" customHeight="1">
-      <c r="B94" s="1"/>
+      <c r="J92" s="1"/>
+    </row>
+    <row r="93" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A93" s="1"/>
+      <c r="B93" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I93" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A94" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>120</v>
+      </c>
       <c r="C94" s="1"/>
-      <c r="I94" s="1"/>
-    </row>
-    <row r="95" ht="13.5" customHeight="1">
-      <c r="A95" s="1"/>
+      <c r="I94" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A95" s="1" t="s">
+        <v>120</v>
+      </c>
       <c r="B95" s="1"/>
-    </row>
-    <row r="96" ht="13.5" customHeight="1">
-      <c r="A96" s="1"/>
-    </row>
-    <row r="97" ht="13.5" customHeight="1">
-      <c r="I97" s="1"/>
-    </row>
-    <row r="98" ht="13.5" customHeight="1">
-      <c r="I98" s="1"/>
-    </row>
-    <row r="99" ht="13.5" customHeight="1">
+      <c r="C95" s="1"/>
+      <c r="I95" s="1"/>
+    </row>
+    <row r="96" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B96" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I96" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A97" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C97" s="1"/>
+      <c r="I97" s="8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A98" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B98" s="1"/>
+    </row>
+    <row r="99" spans="1:9" ht="13.5" customHeight="1">
       <c r="A99" s="1"/>
-      <c r="B99" s="1"/>
-      <c r="I99" s="1"/>
-    </row>
-    <row r="100" ht="13.5" customHeight="1">
-      <c r="A100" s="1"/>
-      <c r="H100" s="1"/>
-      <c r="I100" s="1"/>
-    </row>
-    <row r="101" ht="13.5" customHeight="1">
-      <c r="B101" s="1"/>
+      <c r="B99" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I99" s="8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B100" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I100" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A101" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>113</v>
+      </c>
       <c r="C101" s="1"/>
-      <c r="I101" s="1"/>
-    </row>
-    <row r="102" ht="13.5" customHeight="1">
+      <c r="I101" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A102" s="1" t="s">
+        <v>113</v>
+      </c>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
       <c r="I102" s="1"/>
     </row>
-    <row r="103" ht="13.5" customHeight="1">
-      <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
-      <c r="I103" s="1"/>
-    </row>
-    <row r="104" ht="13.5" customHeight="1">
-      <c r="I104" s="1"/>
-    </row>
-    <row r="105" ht="13.5" customHeight="1">
-      <c r="I105" s="1"/>
-    </row>
-    <row r="106" ht="13.5" customHeight="1">
+    <row r="103" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B103" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I103" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="30.6" customHeight="1">
+      <c r="A104" s="1"/>
+      <c r="B104" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I104" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A105" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I105" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A106" s="1" t="s">
+        <v>130</v>
+      </c>
       <c r="I106" s="1"/>
     </row>
-    <row r="107" ht="13.5" customHeight="1">
-      <c r="I107" s="1"/>
-    </row>
-    <row r="108" ht="13.5" customHeight="1">
-      <c r="B108" s="1"/>
-      <c r="C108" s="1"/>
-      <c r="I108" s="1"/>
-    </row>
-    <row r="109" ht="13.5" customHeight="1">
-      <c r="B109" s="1"/>
-      <c r="C109" s="1"/>
-      <c r="I109" s="1"/>
-    </row>
-    <row r="110" ht="13.5" customHeight="1">
+    <row r="107" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B107" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I107" s="8" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A108" s="1"/>
+      <c r="B108" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I108" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A109" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H109" s="1"/>
+      <c r="I109" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A110" s="1" t="s">
+        <v>134</v>
+      </c>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
       <c r="I110" s="1"/>
     </row>
-    <row r="111" ht="13.5" customHeight="1">
-      <c r="B111" s="1"/>
-      <c r="C111" s="1"/>
-      <c r="I111" s="1"/>
-    </row>
-    <row r="112" ht="13.5" customHeight="1">
-      <c r="B112" s="1"/>
-      <c r="C112" s="1"/>
-      <c r="I112" s="1"/>
-    </row>
-    <row r="113" ht="13.5" customHeight="1">
-      <c r="A113" s="1"/>
-      <c r="B113" s="1"/>
-      <c r="I113" s="1"/>
-      <c r="J113" s="1"/>
-    </row>
-    <row r="114" ht="13.5" customHeight="1">
-      <c r="A114" s="1"/>
-      <c r="B114" s="1"/>
+    <row r="111" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B111" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I111" s="8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B112" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I112" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A113" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I113" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A114" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="I114" s="1"/>
-      <c r="J114" s="1"/>
-    </row>
-    <row r="115" ht="13.5" customHeight="1">
+    </row>
+    <row r="115" spans="1:10" ht="13.5" customHeight="1">
       <c r="A115" s="1"/>
       <c r="I115" s="1"/>
-      <c r="J115" s="1"/>
-    </row>
-    <row r="116" ht="13.5" customHeight="1">
-      <c r="B116" s="1"/>
-      <c r="C116" s="1"/>
+    </row>
+    <row r="116" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A116" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G116">
+        <v>1</v>
+      </c>
       <c r="I116" s="1"/>
     </row>
-    <row r="117" ht="13.5" customHeight="1">
-      <c r="A117" s="1"/>
-      <c r="B117" s="1"/>
-    </row>
-    <row r="118" ht="13.5" customHeight="1">
-      <c r="A118" s="1"/>
-    </row>
-    <row r="119" ht="13.5" customHeight="1">
+    <row r="117" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B117" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I117" s="1"/>
+    </row>
+    <row r="118" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B118" s="1"/>
+      <c r="C118" s="1"/>
+      <c r="I118" s="1"/>
+    </row>
+    <row r="119" spans="1:10" ht="13.5" customHeight="1">
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
       <c r="I119" s="1"/>
     </row>
-    <row r="120" ht="13.5" customHeight="1">
+    <row r="120" spans="1:10" ht="13.5" customHeight="1">
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
       <c r="I120" s="1"/>
     </row>
-    <row r="121" ht="13.5" customHeight="1">
+    <row r="121" spans="1:10" ht="13.5" customHeight="1">
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
       <c r="I121" s="1"/>
     </row>
-    <row r="122" ht="13.5" customHeight="1">
-      <c r="A122" s="1"/>
+    <row r="122" spans="1:10" ht="13.5" customHeight="1">
       <c r="B122" s="1"/>
-    </row>
-    <row r="123" ht="13.5" customHeight="1">
+      <c r="C122" s="1"/>
+      <c r="I122" s="1"/>
+    </row>
+    <row r="123" spans="1:10" ht="13.5" customHeight="1">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="I123" s="1"/>
       <c r="J123" s="1"/>
     </row>
-    <row r="124" ht="13.5" customHeight="1">
+    <row r="124" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A124" s="1"/>
       <c r="B124" s="1"/>
-      <c r="C124" s="1"/>
       <c r="I124" s="1"/>
-    </row>
-    <row r="125" ht="13.5" customHeight="1">
-      <c r="B125" s="1"/>
-      <c r="C125" s="1"/>
+      <c r="J124" s="1"/>
+    </row>
+    <row r="125" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A125" s="1"/>
       <c r="I125" s="1"/>
-    </row>
-    <row r="126" ht="13.5" customHeight="1">
-      <c r="A126" s="1"/>
+      <c r="J125" s="1"/>
+    </row>
+    <row r="126" spans="1:10" ht="13.5" customHeight="1">
       <c r="B126" s="1"/>
-    </row>
-    <row r="127" ht="13.5" customHeight="1">
+      <c r="C126" s="1"/>
+      <c r="I126" s="1"/>
+    </row>
+    <row r="127" spans="1:10" ht="13.5" customHeight="1">
       <c r="A127" s="1"/>
-    </row>
-    <row r="128" ht="13.5" customHeight="1">
-      <c r="I128" s="1"/>
-    </row>
-    <row r="129" ht="13.5" customHeight="1">
-      <c r="A129" s="1"/>
-    </row>
-    <row r="130" ht="13.5" customHeight="1">
-      <c r="A130" s="1"/>
-    </row>
-    <row r="131" ht="13.5" customHeight="1">
-      <c r="A131" s="1"/>
+      <c r="B127" s="1"/>
+    </row>
+    <row r="128" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A128" s="1"/>
+    </row>
+    <row r="129" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="I129" s="1"/>
+    </row>
+    <row r="130" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B130" s="1"/>
+      <c r="C130" s="1"/>
+      <c r="I130" s="1"/>
+    </row>
+    <row r="131" spans="1:10" ht="13.5" customHeight="1">
       <c r="B131" s="1"/>
-      <c r="H131" s="1"/>
+      <c r="C131" s="1"/>
       <c r="I131" s="1"/>
     </row>
-    <row r="132" ht="13.5" customHeight="1">
+    <row r="132" spans="1:10" ht="13.5" customHeight="1">
       <c r="A132" s="1"/>
-      <c r="H132" s="1"/>
-      <c r="I132" s="1"/>
-    </row>
-    <row r="133" ht="13.5" customHeight="1">
+      <c r="B132" s="1"/>
+    </row>
+    <row r="133" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A133" s="1"/>
+      <c r="B133" s="1"/>
       <c r="I133" s="1"/>
-    </row>
-    <row r="134" ht="13.5" customHeight="1">
+      <c r="J133" s="1"/>
+    </row>
+    <row r="134" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B134" s="1"/>
+      <c r="C134" s="1"/>
       <c r="I134" s="1"/>
     </row>
-    <row r="135" ht="13.5" customHeight="1">
+    <row r="135" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B135" s="1"/>
+      <c r="C135" s="1"/>
       <c r="I135" s="1"/>
     </row>
-    <row r="136" ht="13.5" customHeight="1">
-      <c r="I136" s="1"/>
-    </row>
-    <row r="137" ht="13.5" customHeight="1">
-      <c r="I137" s="1"/>
-    </row>
-    <row r="138" ht="13.5" customHeight="1">
+    <row r="136" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A136" s="1"/>
+      <c r="B136" s="1"/>
+    </row>
+    <row r="137" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A137" s="1"/>
+    </row>
+    <row r="138" spans="1:10" ht="13.5" customHeight="1">
       <c r="I138" s="1"/>
     </row>
-    <row r="139" ht="13.5" customHeight="1">
-      <c r="I139" s="1"/>
-    </row>
-    <row r="140" ht="13.5" customHeight="1"/>
-    <row r="141" ht="13.5" customHeight="1"/>
-    <row r="142" ht="13.5" customHeight="1"/>
-    <row r="143" ht="13.5" customHeight="1"/>
-    <row r="144" ht="13.5" customHeight="1"/>
-    <row r="145" ht="13.5" customHeight="1"/>
-    <row r="146" ht="13.5" customHeight="1"/>
-    <row r="147" ht="13.5" customHeight="1"/>
-    <row r="148" ht="13.5" customHeight="1"/>
-    <row r="149" ht="13.5" customHeight="1"/>
-    <row r="150" ht="13.5" customHeight="1"/>
-    <row r="151" ht="13.5" customHeight="1"/>
-    <row r="152" ht="13.5" customHeight="1"/>
-    <row r="153" ht="13.5" customHeight="1"/>
-    <row r="154" ht="13.5" customHeight="1"/>
-    <row r="155" ht="13.5" customHeight="1"/>
-    <row r="156" ht="13.5" customHeight="1"/>
-    <row r="157" ht="13.5" customHeight="1"/>
-    <row r="158" ht="13.5" customHeight="1"/>
-    <row r="159" ht="13.5" customHeight="1"/>
-    <row r="160" ht="13.5" customHeight="1"/>
+    <row r="139" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A139" s="1"/>
+    </row>
+    <row r="140" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A140" s="1"/>
+    </row>
+    <row r="141" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A141" s="1"/>
+      <c r="B141" s="1"/>
+      <c r="H141" s="1"/>
+      <c r="I141" s="1"/>
+    </row>
+    <row r="142" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A142" s="1"/>
+      <c r="H142" s="1"/>
+      <c r="I142" s="1"/>
+    </row>
+    <row r="143" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I143" s="1"/>
+    </row>
+    <row r="144" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I144" s="1"/>
+    </row>
+    <row r="145" spans="9:9" ht="13.5" customHeight="1">
+      <c r="I145" s="1"/>
+    </row>
+    <row r="146" spans="9:9" ht="13.5" customHeight="1">
+      <c r="I146" s="1"/>
+    </row>
+    <row r="147" spans="9:9" ht="13.5" customHeight="1">
+      <c r="I147" s="1"/>
+    </row>
+    <row r="148" spans="9:9" ht="13.5" customHeight="1">
+      <c r="I148" s="1"/>
+    </row>
+    <row r="149" spans="9:9" ht="13.5" customHeight="1">
+      <c r="I149" s="1"/>
+    </row>
+    <row r="150" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="151" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="152" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="153" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="154" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="155" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="156" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="157" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="158" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="159" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="160" spans="9:9" ht="13.5" customHeight="1"/>
     <row r="161" ht="13.5" customHeight="1"/>
     <row r="162" ht="13.5" customHeight="1"/>
     <row r="163" ht="13.5" customHeight="1"/>
@@ -1107,22 +2417,29 @@
     <row r="190" ht="13.5" customHeight="1"/>
     <row r="191" ht="13.5" customHeight="1"/>
     <row r="192" ht="13.5" customHeight="1"/>
-    <row r="193" ht="13.5" customHeight="1"/>
-    <row r="194" ht="13.5" customHeight="1"/>
-    <row r="195" ht="13.5" customHeight="1"/>
-    <row r="196" ht="13.5" customHeight="1"/>
-    <row r="197" ht="13.5" customHeight="1"/>
-    <row r="198" ht="13.5" customHeight="1"/>
-    <row r="199" ht="13.5" customHeight="1"/>
-    <row r="200" ht="13.5" customHeight="1"/>
-    <row r="201" ht="13.5" customHeight="1"/>
-    <row r="202" ht="13.5" customHeight="1"/>
-    <row r="203" ht="13.5" customHeight="1"/>
-    <row r="204" ht="13.5" customHeight="1"/>
-    <row r="205" ht="13.5" customHeight="1"/>
-    <row r="206" ht="13.5" customHeight="1"/>
-    <row r="207" ht="13.5" customHeight="1"/>
-    <row r="208" ht="13.5" customHeight="1"/>
+    <row r="193" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="194" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="195" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="196" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="197" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="198" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="199" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="200" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="201" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="202" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="203" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="204" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="205" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="206" spans="1:2" ht="13.5" customHeight="1">
+      <c r="A206" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="208" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="209" ht="13.5" customHeight="1"/>
     <row r="210" ht="13.5" customHeight="1"/>
     <row r="211" ht="13.5" customHeight="1"/>
@@ -1973,10 +3290,19 @@
     <row r="1056" ht="13.5" customHeight="1"/>
     <row r="1057" ht="13.5" customHeight="1"/>
     <row r="1058" ht="13.5" customHeight="1"/>
+    <row r="1059" ht="13.5" customHeight="1"/>
+    <row r="1060" ht="13.5" customHeight="1"/>
+    <row r="1061" ht="13.5" customHeight="1"/>
+    <row r="1062" ht="13.5" customHeight="1"/>
+    <row r="1063" ht="13.5" customHeight="1"/>
+    <row r="1064" ht="13.5" customHeight="1"/>
+    <row r="1065" ht="13.5" customHeight="1"/>
+    <row r="1066" ht="13.5" customHeight="1"/>
+    <row r="1067" ht="13.5" customHeight="1"/>
+    <row r="1068" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="4"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/test260903/chapter0205.xlsx
+++ b/Assets/test260903/chapter0205.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="314" documentId="11_8E1AFE78FBD34A042E83A027A8BF20349734C0B7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FF6ED99-642B-464F-9370-6D1E9BDBACA9}"/>
+  <xr:revisionPtr revIDLastSave="334" documentId="11_8E1AFE78FBD34A042E83A027A8BF20349734C0B7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BE1FEFD-2B2F-4C6A-99C4-2D08E17A1BA8}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="147">
   <si>
     <t>Command</t>
   </si>
@@ -645,6 +645,28 @@
   <si>
     <t>FadeOut</t>
     <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Bgm</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>BGM_バトル</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>StopBgm</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>BGM_緊迫</t>
+  </si>
+  <si>
+    <t>BGM_不穏</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>BGM_決意</t>
   </si>
 </sst>
 </file>
@@ -960,7 +982,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1068"/>
+  <dimension ref="A1:L1073"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
@@ -1063,7 +1085,12 @@
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:12" ht="13.5" customHeight="1">
-      <c r="B6" s="1"/>
+      <c r="A6" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1" t="s">
         <v>16</v>
@@ -1139,172 +1166,163 @@
       </c>
       <c r="I14" s="8"/>
     </row>
-    <row r="15" spans="1:12" ht="30.6" customHeight="1">
-      <c r="I15" s="8" t="s">
+    <row r="15" spans="1:12" ht="30" customHeight="1">
+      <c r="A15" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="I15" s="8"/>
+    </row>
+    <row r="16" spans="1:12" ht="30.6" customHeight="1">
+      <c r="I16" s="8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="30.6" customHeight="1">
-      <c r="A16" s="9" t="s">
+    <row r="17" spans="1:10" ht="30.6" customHeight="1">
+      <c r="A17" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B17" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="I16" s="8"/>
-    </row>
-    <row r="17" spans="1:10" ht="30" customHeight="1">
-      <c r="B17" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="5" t="s">
+      <c r="I17" s="8"/>
+    </row>
+    <row r="18" spans="1:10" ht="30.6" customHeight="1">
+      <c r="A18" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="I18" s="8"/>
+    </row>
+    <row r="19" spans="1:10" ht="30" customHeight="1">
+      <c r="B19" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="I19" s="8" t="s">
         <v>30</v>
-      </c>
-      <c r="J17" s="1"/>
-    </row>
-    <row r="18" spans="1:10" ht="30" customHeight="1">
-      <c r="A18" s="1"/>
-      <c r="B18" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G18" s="1"/>
-      <c r="I18" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="J18" s="1"/>
-    </row>
-    <row r="19" spans="1:10" ht="28.2" customHeight="1">
-      <c r="A19" s="1"/>
-      <c r="B19" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>35</v>
       </c>
       <c r="J19" s="1"/>
     </row>
     <row r="20" spans="1:10" ht="30" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" s="1"/>
       <c r="I20" s="8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J20" s="1"/>
     </row>
     <row r="21" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A21" s="1"/>
       <c r="B21" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>37</v>
+      </c>
       <c r="I21" s="8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J21" s="1"/>
     </row>
-    <row r="22" spans="1:10" ht="30.6" customHeight="1">
+    <row r="22" spans="1:10" ht="30" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="5" t="s">
         <v>39</v>
       </c>
+      <c r="C22" s="1"/>
       <c r="I22" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="27.6" customHeight="1">
-      <c r="A23" s="1"/>
+        <v>38</v>
+      </c>
+      <c r="J22" s="1"/>
+    </row>
+    <row r="23" spans="1:10" ht="28.2" customHeight="1">
       <c r="B23" s="5" t="s">
         <v>39</v>
       </c>
+      <c r="C23" s="1"/>
       <c r="I23" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="28.8" customHeight="1">
+        <v>40</v>
+      </c>
+      <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="1:10" ht="30.6" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="30" customHeight="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="27.6" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A26" s="1"/>
+      <c r="B26" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C26" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="H25" s="1"/>
-      <c r="I25" s="8" t="s">
+      <c r="I26" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="30" customHeight="1">
+      <c r="A27" s="1"/>
+      <c r="B27" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H27" s="1"/>
+      <c r="I27" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="30" customHeight="1">
-      <c r="B26" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26" s="6" t="s">
+    <row r="28" spans="1:10" ht="30" customHeight="1">
+      <c r="B28" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="I26" s="8" t="s">
+      <c r="I28" s="8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="28.2" customHeight="1">
-      <c r="B27" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="6" t="s">
+    <row r="29" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="I27" s="8" t="s">
+      <c r="I29" s="8" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A28" s="1"/>
-      <c r="B28" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="J28" s="1"/>
-    </row>
-    <row r="29" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A29" s="1"/>
-      <c r="B29" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I29" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J29" s="1"/>
-    </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A30" s="1"/>
       <c r="B30" s="5" t="s">
         <v>36</v>
       </c>
@@ -1312,10 +1330,12 @@
         <v>37</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="13.5" customHeight="1">
+        <v>48</v>
+      </c>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A31" s="1"/>
       <c r="B31" s="5" t="s">
         <v>31</v>
       </c>
@@ -1323,90 +1343,96 @@
         <v>50</v>
       </c>
       <c r="I31" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B32" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B33" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I33" s="8" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A32" s="7" t="s">
+    <row r="34" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A34" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B34" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C32" s="6"/>
-      <c r="I32" s="8"/>
-    </row>
-    <row r="33" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A33" s="1"/>
-      <c r="B33" s="5" t="s">
+      <c r="C34" s="6"/>
+      <c r="I34" s="8"/>
+    </row>
+    <row r="35" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A35" s="1"/>
+      <c r="B35" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C35" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="I33" s="8" t="s">
+      <c r="I35" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="J33" s="1"/>
-    </row>
-    <row r="34" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A34" s="1"/>
-      <c r="B34" s="5" t="s">
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A36" s="1"/>
+      <c r="B36" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C36" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-    </row>
-    <row r="35" spans="1:10" ht="27.6" customHeight="1">
-      <c r="B35" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="6" t="s">
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B37" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="I35" s="8" t="s">
+      <c r="I37" s="8" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B36" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C36" s="6" t="s">
+    <row r="38" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B38" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="I36" s="8" t="s">
+      <c r="I38" s="8" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A37" s="7" t="s">
+    <row r="39" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A39" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B39" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C37" s="6"/>
-      <c r="I37" s="8"/>
-    </row>
-    <row r="38" spans="1:10" ht="28.2" customHeight="1">
-      <c r="B38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I38" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="28.2" customHeight="1">
-      <c r="B39" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>62</v>
-      </c>
+      <c r="C39" s="6"/>
       <c r="I39" s="8"/>
     </row>
     <row r="40" spans="1:10" ht="28.2" customHeight="1">
@@ -1414,151 +1440,144 @@
         <v>39</v>
       </c>
       <c r="I40" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B41" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I41" s="8"/>
+    </row>
+    <row r="42" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B42" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I42" s="8" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="30.6" customHeight="1">
-      <c r="B41" s="5" t="s">
+    <row r="43" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B43" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="I41" s="8" t="s">
+      <c r="I43" s="8" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B42" s="5" t="s">
+    <row r="44" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B44" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C44" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="I42" s="8" t="s">
+      <c r="I44" s="8" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="30" customHeight="1">
-      <c r="B43" s="5" t="s">
+    <row r="45" spans="1:10" ht="30" customHeight="1">
+      <c r="B45" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C45" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="I43" s="8" t="s">
+      <c r="I45" s="8" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="28.2" customHeight="1">
-      <c r="B44" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="5" t="s">
+    <row r="46" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B46" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I44" s="8" t="s">
+      <c r="I46" s="8" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="27.6" customHeight="1">
-      <c r="B45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="5" t="s">
+    <row r="47" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B47" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I45" s="8" t="s">
+      <c r="I47" s="8" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="I46" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="30" customHeight="1">
-      <c r="B47" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I47" s="8" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="28.8" customHeight="1">
       <c r="B48" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="30" customHeight="1">
+      <c r="B49" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C49" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="I48" s="8" t="s">
+      <c r="I49" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B50" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I50" s="8" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A49" s="7" t="s">
+    <row r="51" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A51" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B51" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C49" s="5"/>
-      <c r="I49" s="8"/>
-    </row>
-    <row r="50" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B50" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I50" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B51" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I51" s="8" t="s">
-        <v>74</v>
-      </c>
+      <c r="C51" s="5"/>
+      <c r="I51" s="8"/>
     </row>
     <row r="52" spans="1:10" ht="13.5" customHeight="1">
       <c r="B52" s="5" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A53" s="1"/>
       <c r="B53" s="5" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="31.8" customHeight="1">
-      <c r="A54" s="1"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="13.5" customHeight="1">
       <c r="B54" s="5" t="s">
         <v>76</v>
       </c>
@@ -1566,7 +1585,7 @@
         <v>55</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="28.8" customHeight="1">
@@ -1578,11 +1597,11 @@
         <v>55</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="J55" s="1"/>
-    </row>
-    <row r="56" spans="1:10" ht="28.8" customHeight="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="31.8" customHeight="1">
+      <c r="A56" s="1"/>
       <c r="B56" s="5" t="s">
         <v>76</v>
       </c>
@@ -1590,60 +1609,59 @@
         <v>55</v>
       </c>
       <c r="I56" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A57" s="1"/>
+      <c r="B57" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="J57" s="1"/>
+    </row>
+    <row r="58" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B58" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I58" s="8" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="28.2" customHeight="1">
-      <c r="B57" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="5" t="s">
+    <row r="59" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I57" s="8" t="s">
+      <c r="I59" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="J57" s="1"/>
-    </row>
-    <row r="58" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B58" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="5" t="s">
+      <c r="J59" s="1"/>
+    </row>
+    <row r="60" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I58" s="8" t="s">
+      <c r="I60" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="J58" s="1"/>
-    </row>
-    <row r="59" spans="1:10" ht="30" customHeight="1">
-      <c r="A59" s="1"/>
-      <c r="B59" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="I59" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="J59" s="1"/>
-    </row>
-    <row r="60" spans="1:10" ht="30" customHeight="1">
-      <c r="A60" s="1"/>
-      <c r="B60" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="I60" s="8" t="s">
-        <v>84</v>
-      </c>
       <c r="J60" s="1"/>
     </row>
-    <row r="61" spans="1:10" ht="13.5" customHeight="1">
+    <row r="61" spans="1:10" ht="30" customHeight="1">
+      <c r="A61" s="1"/>
       <c r="B61" s="5" t="s">
         <v>31</v>
       </c>
@@ -1651,10 +1669,12 @@
         <v>50</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="28.2" customHeight="1">
+        <v>83</v>
+      </c>
+      <c r="J61" s="1"/>
+    </row>
+    <row r="62" spans="1:10" ht="30" customHeight="1">
+      <c r="A62" s="1"/>
       <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
@@ -1662,11 +1682,11 @@
         <v>50</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A63" s="1"/>
+        <v>84</v>
+      </c>
+      <c r="J62" s="1"/>
+    </row>
+    <row r="63" spans="1:10" ht="13.5" customHeight="1">
       <c r="B63" s="5" t="s">
         <v>31</v>
       </c>
@@ -1674,11 +1694,10 @@
         <v>50</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A64" s="1"/>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="28.2" customHeight="1">
       <c r="B64" s="5" t="s">
         <v>31</v>
       </c>
@@ -1686,33 +1705,34 @@
         <v>50</v>
       </c>
       <c r="I64" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A65" s="1"/>
+      <c r="B65" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I65" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A66" s="1"/>
+      <c r="B66" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I66" s="8" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="28.2" customHeight="1">
-      <c r="B65" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I65" s="8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B66" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I66" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A67" s="1"/>
+    <row r="67" spans="1:9" ht="28.2" customHeight="1">
       <c r="B67" s="5" t="s">
         <v>61</v>
       </c>
@@ -1720,11 +1740,10 @@
         <v>65</v>
       </c>
       <c r="I67" s="8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="30.6" customHeight="1">
-      <c r="A68" s="1"/>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="13.5" customHeight="1">
       <c r="B68" s="5" t="s">
         <v>61</v>
       </c>
@@ -1732,21 +1751,19 @@
         <v>65</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B69" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I69" s="8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="28.8" customHeight="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A69" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B69" s="5"/>
+      <c r="C69" s="5"/>
+      <c r="I69" s="8"/>
+    </row>
+    <row r="70" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A70" s="1"/>
       <c r="B70" s="5" t="s">
         <v>61</v>
       </c>
@@ -1754,21 +1771,21 @@
         <v>65</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" ht="30.6" customHeight="1">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A71" s="5" t="s">
+        <v>141</v>
+      </c>
       <c r="B71" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I71" s="8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" ht="28.8" customHeight="1">
+        <v>145</v>
+      </c>
+      <c r="C71" s="5"/>
+      <c r="I71" s="8"/>
+    </row>
+    <row r="72" spans="1:9" ht="30.6" customHeight="1">
+      <c r="A72" s="1"/>
       <c r="B72" s="5" t="s">
         <v>61</v>
       </c>
@@ -1776,11 +1793,10 @@
         <v>65</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" ht="30" customHeight="1">
-      <c r="A73" s="1"/>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="28.8" customHeight="1">
       <c r="B73" s="5" t="s">
         <v>61</v>
       </c>
@@ -1788,23 +1804,21 @@
         <v>65</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A74" s="1"/>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="28.8" customHeight="1">
       <c r="B74" s="5" t="s">
         <v>61</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="H74" s="1"/>
       <c r="I74" s="8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" ht="30" customHeight="1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="30.6" customHeight="1">
       <c r="B75" s="5" t="s">
         <v>61</v>
       </c>
@@ -1812,92 +1826,99 @@
         <v>65</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" ht="13.5" customHeight="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="28.8" customHeight="1">
       <c r="B76" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C76" s="1"/>
+        <v>61</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>65</v>
+      </c>
       <c r="I76" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" ht="31.8" customHeight="1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="30" customHeight="1">
       <c r="A77" s="1"/>
       <c r="B77" s="5" t="s">
-        <v>39</v>
+        <v>61</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ht="31.8" customHeight="1">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="13.5" customHeight="1">
       <c r="A78" s="1"/>
       <c r="B78" s="5" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="30" customHeight="1">
+      <c r="B79" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I79" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B80" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C80" s="1"/>
+      <c r="I80" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="31.8" customHeight="1">
+      <c r="A81" s="1"/>
+      <c r="B81" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I81" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="31.8" customHeight="1">
+      <c r="A82" s="1"/>
+      <c r="B82" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H82" s="1"/>
+      <c r="I82" s="8" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="28.2" customHeight="1">
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="5" t="s">
+    <row r="83" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B83" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="I79" s="8" t="s">
+      <c r="I83" s="8" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="I80" s="8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" ht="30" customHeight="1">
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="I81" s="8" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B82" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C82" s="1"/>
-      <c r="I82" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" ht="30" customHeight="1">
-      <c r="B83" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C83" s="1"/>
-      <c r="I83" s="8" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" ht="13.5" customHeight="1">
+    <row r="84" spans="1:10" ht="28.8" customHeight="1">
       <c r="B84" s="5" t="s">
         <v>31</v>
       </c>
@@ -1905,16 +1926,18 @@
         <v>50</v>
       </c>
       <c r="I84" s="8" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" ht="28.2" customHeight="1">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="30" customHeight="1">
       <c r="B85" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C85" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="I85" s="8" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="13.5" customHeight="1">
@@ -1923,185 +1946,180 @@
       </c>
       <c r="C86" s="1"/>
       <c r="I86" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="30" customHeight="1">
+      <c r="B87" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C87" s="1"/>
+      <c r="I87" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B88" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I88" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B89" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C89" s="1"/>
+      <c r="I89" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B90" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C90" s="1"/>
+      <c r="I90" s="8" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B87" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C87" s="5" t="s">
+    <row r="91" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B91" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C91" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="I87" s="8" t="s">
+      <c r="I91" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="J87" s="1"/>
-    </row>
-    <row r="88" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A88" s="10" t="s">
+      <c r="J91" s="1"/>
+    </row>
+    <row r="92" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A92" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C92" s="5"/>
+      <c r="I92" s="8"/>
+      <c r="J92" s="1"/>
+    </row>
+    <row r="93" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A93" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B93" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="I88" s="8" t="s">
+      <c r="I93" s="8" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A89" s="1" t="s">
+    <row r="94" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A94" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="I89" s="1"/>
-    </row>
-    <row r="90" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B90" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C90" s="5" t="s">
+      <c r="I94" s="1"/>
+    </row>
+    <row r="95" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B95" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C95" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="I90" s="8" t="s">
+      <c r="I95" s="8" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A91" s="10" t="s">
+    <row r="96" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A96" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B96" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="I91" s="8" t="s">
+      <c r="I96" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="J91" s="1"/>
-    </row>
-    <row r="92" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A92" s="1" t="s">
+      <c r="J96" s="1"/>
+    </row>
+    <row r="97" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A97" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B92" s="1"/>
-      <c r="I92" s="1"/>
-      <c r="J92" s="1"/>
-    </row>
-    <row r="93" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A93" s="1"/>
-      <c r="B93" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C93" s="5" t="s">
+      <c r="B97" s="1"/>
+      <c r="I97" s="1"/>
+      <c r="J97" s="1"/>
+    </row>
+    <row r="98" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A98" s="1"/>
+      <c r="B98" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C98" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="I93" s="8" t="s">
+      <c r="I98" s="8" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A94" s="10" t="s">
+    <row r="99" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A99" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B99" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C94" s="1"/>
-      <c r="I94" s="8" t="s">
+      <c r="C99" s="1"/>
+      <c r="I99" s="8" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A95" s="1" t="s">
+    <row r="100" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A100" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B95" s="1"/>
-      <c r="C95" s="1"/>
-      <c r="I95" s="1"/>
-    </row>
-    <row r="96" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B96" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C96" s="5" t="s">
+      <c r="B100" s="1"/>
+      <c r="C100" s="1"/>
+      <c r="I100" s="1"/>
+    </row>
+    <row r="101" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B101" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C101" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I96" s="8" t="s">
+      <c r="I101" s="8" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A97" s="10" t="s">
+    <row r="102" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A102" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B102" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C97" s="1"/>
-      <c r="I97" s="8" t="s">
+      <c r="C102" s="1"/>
+      <c r="I102" s="8" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A98" s="1" t="s">
+    <row r="103" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A103" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B98" s="1"/>
-    </row>
-    <row r="99" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A99" s="1"/>
-      <c r="B99" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I99" s="8" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" ht="28.2" customHeight="1">
-      <c r="B100" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I100" s="8" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A101" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C101" s="1"/>
-      <c r="I101" s="8" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A102" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B102" s="1"/>
-      <c r="C102" s="1"/>
-      <c r="I102" s="1"/>
-    </row>
-    <row r="103" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B103" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I103" s="8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B103" s="1"/>
+    </row>
+    <row r="104" spans="1:10" ht="13.5" customHeight="1">
       <c r="A104" s="1"/>
       <c r="B104" s="5" t="s">
         <v>31</v>
@@ -2109,40 +2127,42 @@
       <c r="C104" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I104" s="11" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A105" s="10" t="s">
+      <c r="I104" s="8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B105" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I105" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A106" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="I105" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A106" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="I106" s="1"/>
-    </row>
-    <row r="107" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B107" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I107" s="8" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A108" s="1"/>
+      <c r="B106" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C106" s="1"/>
+      <c r="I106" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A107" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B107" s="1"/>
+      <c r="C107" s="1"/>
+      <c r="I107" s="1"/>
+    </row>
+    <row r="108" spans="1:10" ht="13.5" customHeight="1">
       <c r="B108" s="5" t="s">
         <v>31</v>
       </c>
@@ -2150,41 +2170,39 @@
         <v>32</v>
       </c>
       <c r="I108" s="8" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A109" s="10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="30.6" customHeight="1">
+      <c r="A109" s="1"/>
+      <c r="B109" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I109" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A110" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="H109" s="1"/>
-      <c r="I109" s="8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A110" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B110" s="1"/>
-      <c r="C110" s="1"/>
-      <c r="I110" s="1"/>
-    </row>
-    <row r="111" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B111" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I111" s="8" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B110" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I110" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A111" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I111" s="1"/>
+    </row>
+    <row r="112" spans="1:10" ht="28.8" customHeight="1">
       <c r="B112" s="5" t="s">
         <v>31</v>
       </c>
@@ -2192,92 +2210,122 @@
         <v>32</v>
       </c>
       <c r="I112" s="8" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A113" s="1"/>
+      <c r="B113" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I113" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A114" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H114" s="1"/>
+      <c r="I114" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A115" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B115" s="1"/>
+      <c r="C115" s="1"/>
+      <c r="I115" s="1"/>
+    </row>
+    <row r="116" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B116" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I116" s="8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B117" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I117" s="8" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A113" s="10" t="s">
+    <row r="118" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A118" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="B118" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I113" s="8" t="s">
+      <c r="I118" s="8" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A114" s="1" t="s">
+    <row r="119" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A119" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I114" s="1"/>
-    </row>
-    <row r="115" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A115" s="1"/>
-      <c r="I115" s="1"/>
-    </row>
-    <row r="116" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A116" s="6" t="s">
+      <c r="I119" s="1"/>
+    </row>
+    <row r="120" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A120" s="1"/>
+      <c r="I120" s="1"/>
+    </row>
+    <row r="121" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A121" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="B116" s="6" t="s">
+      <c r="B121" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G116">
+      <c r="G121">
         <v>1</v>
       </c>
-      <c r="I116" s="1"/>
-    </row>
-    <row r="117" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B117" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C117" s="5" t="s">
+      <c r="I121" s="1"/>
+    </row>
+    <row r="122" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B122" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C122" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="I117" s="1"/>
-    </row>
-    <row r="118" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B118" s="1"/>
-      <c r="C118" s="1"/>
-      <c r="I118" s="1"/>
-    </row>
-    <row r="119" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B119" s="1"/>
-      <c r="C119" s="1"/>
-      <c r="I119" s="1"/>
-    </row>
-    <row r="120" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B120" s="1"/>
-      <c r="C120" s="1"/>
-      <c r="I120" s="1"/>
-    </row>
-    <row r="121" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B121" s="1"/>
-      <c r="C121" s="1"/>
-      <c r="I121" s="1"/>
-    </row>
-    <row r="122" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B122" s="1"/>
-      <c r="C122" s="1"/>
       <c r="I122" s="1"/>
     </row>
     <row r="123" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A123" s="1"/>
+      <c r="A123" s="5" t="s">
+        <v>143</v>
+      </c>
       <c r="B123" s="1"/>
+      <c r="C123" s="1"/>
       <c r="I123" s="1"/>
-      <c r="J123" s="1"/>
     </row>
     <row r="124" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A124" s="1"/>
       <c r="B124" s="1"/>
+      <c r="C124" s="1"/>
       <c r="I124" s="1"/>
-      <c r="J124" s="1"/>
     </row>
     <row r="125" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A125" s="1"/>
+      <c r="B125" s="1"/>
+      <c r="C125" s="1"/>
       <c r="I125" s="1"/>
-      <c r="J125" s="1"/>
     </row>
     <row r="126" spans="1:10" ht="13.5" customHeight="1">
       <c r="B126" s="1"/>
@@ -2285,21 +2333,26 @@
       <c r="I126" s="1"/>
     </row>
     <row r="127" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A127" s="1"/>
       <c r="B127" s="1"/>
+      <c r="C127" s="1"/>
+      <c r="I127" s="1"/>
     </row>
     <row r="128" spans="1:10" ht="13.5" customHeight="1">
       <c r="A128" s="1"/>
+      <c r="B128" s="1"/>
+      <c r="I128" s="1"/>
+      <c r="J128" s="1"/>
     </row>
     <row r="129" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A129" s="1"/>
       <c r="B129" s="1"/>
-      <c r="C129" s="1"/>
       <c r="I129" s="1"/>
+      <c r="J129" s="1"/>
     </row>
     <row r="130" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B130" s="1"/>
-      <c r="C130" s="1"/>
+      <c r="A130" s="1"/>
       <c r="I130" s="1"/>
+      <c r="J130" s="1"/>
     </row>
     <row r="131" spans="1:10" ht="13.5" customHeight="1">
       <c r="B131" s="1"/>
@@ -2312,9 +2365,6 @@
     </row>
     <row r="133" spans="1:10" ht="13.5" customHeight="1">
       <c r="A133" s="1"/>
-      <c r="B133" s="1"/>
-      <c r="I133" s="1"/>
-      <c r="J133" s="1"/>
     </row>
     <row r="134" spans="1:10" ht="13.5" customHeight="1">
       <c r="B134" s="1"/>
@@ -2327,64 +2377,84 @@
       <c r="I135" s="1"/>
     </row>
     <row r="136" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A136" s="1"/>
       <c r="B136" s="1"/>
+      <c r="C136" s="1"/>
+      <c r="I136" s="1"/>
     </row>
     <row r="137" spans="1:10" ht="13.5" customHeight="1">
       <c r="A137" s="1"/>
+      <c r="B137" s="1"/>
     </row>
     <row r="138" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A138" s="1"/>
+      <c r="B138" s="1"/>
       <c r="I138" s="1"/>
+      <c r="J138" s="1"/>
     </row>
     <row r="139" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A139" s="1"/>
+      <c r="B139" s="1"/>
+      <c r="C139" s="1"/>
+      <c r="I139" s="1"/>
     </row>
     <row r="140" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A140" s="1"/>
+      <c r="B140" s="1"/>
+      <c r="C140" s="1"/>
+      <c r="I140" s="1"/>
     </row>
     <row r="141" spans="1:10" ht="13.5" customHeight="1">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
-      <c r="H141" s="1"/>
-      <c r="I141" s="1"/>
     </row>
     <row r="142" spans="1:10" ht="13.5" customHeight="1">
       <c r="A142" s="1"/>
-      <c r="H142" s="1"/>
-      <c r="I142" s="1"/>
     </row>
     <row r="143" spans="1:10" ht="13.5" customHeight="1">
       <c r="I143" s="1"/>
     </row>
     <row r="144" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I144" s="1"/>
-    </row>
-    <row r="145" spans="9:9" ht="13.5" customHeight="1">
-      <c r="I145" s="1"/>
-    </row>
-    <row r="146" spans="9:9" ht="13.5" customHeight="1">
+      <c r="A144" s="1"/>
+    </row>
+    <row r="145" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A145" s="1"/>
+    </row>
+    <row r="146" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A146" s="1"/>
+      <c r="B146" s="1"/>
+      <c r="H146" s="1"/>
       <c r="I146" s="1"/>
     </row>
-    <row r="147" spans="9:9" ht="13.5" customHeight="1">
+    <row r="147" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A147" s="1"/>
+      <c r="H147" s="1"/>
       <c r="I147" s="1"/>
     </row>
-    <row r="148" spans="9:9" ht="13.5" customHeight="1">
+    <row r="148" spans="1:9" ht="13.5" customHeight="1">
       <c r="I148" s="1"/>
     </row>
-    <row r="149" spans="9:9" ht="13.5" customHeight="1">
+    <row r="149" spans="1:9" ht="13.5" customHeight="1">
       <c r="I149" s="1"/>
     </row>
-    <row r="150" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="151" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="152" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="153" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="154" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="155" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="156" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="157" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="158" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="159" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="160" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="150" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I150" s="1"/>
+    </row>
+    <row r="151" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I151" s="1"/>
+    </row>
+    <row r="152" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I152" s="1"/>
+    </row>
+    <row r="153" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I153" s="1"/>
+    </row>
+    <row r="154" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I154" s="1"/>
+    </row>
+    <row r="155" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="156" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="157" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="158" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="159" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="160" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="161" ht="13.5" customHeight="1"/>
     <row r="162" ht="13.5" customHeight="1"/>
     <row r="163" ht="13.5" customHeight="1"/>
@@ -2417,45 +2487,45 @@
     <row r="190" ht="13.5" customHeight="1"/>
     <row r="191" ht="13.5" customHeight="1"/>
     <row r="192" ht="13.5" customHeight="1"/>
-    <row r="193" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="194" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="195" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="196" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="197" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="198" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="199" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="200" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="201" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="202" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="203" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="204" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="205" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="206" spans="1:2" ht="13.5" customHeight="1">
-      <c r="A206" s="1" t="s">
+    <row r="193" ht="13.5" customHeight="1"/>
+    <row r="194" ht="13.5" customHeight="1"/>
+    <row r="195" ht="13.5" customHeight="1"/>
+    <row r="196" ht="13.5" customHeight="1"/>
+    <row r="197" ht="13.5" customHeight="1"/>
+    <row r="198" ht="13.5" customHeight="1"/>
+    <row r="199" ht="13.5" customHeight="1"/>
+    <row r="200" ht="13.5" customHeight="1"/>
+    <row r="201" ht="13.5" customHeight="1"/>
+    <row r="202" ht="13.5" customHeight="1"/>
+    <row r="203" ht="13.5" customHeight="1"/>
+    <row r="204" ht="13.5" customHeight="1"/>
+    <row r="205" ht="13.5" customHeight="1"/>
+    <row r="206" ht="13.5" customHeight="1"/>
+    <row r="207" ht="13.5" customHeight="1"/>
+    <row r="208" ht="13.5" customHeight="1"/>
+    <row r="209" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="210" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="211" spans="1:2" ht="13.5" customHeight="1">
+      <c r="A211" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B206" s="1" t="s">
+      <c r="B211" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="207" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="208" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="209" ht="13.5" customHeight="1"/>
-    <row r="210" ht="13.5" customHeight="1"/>
-    <row r="211" ht="13.5" customHeight="1"/>
-    <row r="212" ht="13.5" customHeight="1"/>
-    <row r="213" ht="13.5" customHeight="1"/>
-    <row r="214" ht="13.5" customHeight="1"/>
-    <row r="215" ht="13.5" customHeight="1"/>
-    <row r="216" ht="13.5" customHeight="1"/>
-    <row r="217" ht="13.5" customHeight="1"/>
-    <row r="218" ht="13.5" customHeight="1"/>
-    <row r="219" ht="13.5" customHeight="1"/>
-    <row r="220" ht="13.5" customHeight="1"/>
-    <row r="221" ht="13.5" customHeight="1"/>
-    <row r="222" ht="13.5" customHeight="1"/>
-    <row r="223" ht="13.5" customHeight="1"/>
-    <row r="224" ht="13.5" customHeight="1"/>
+    <row r="212" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="213" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="214" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="215" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="216" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="217" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="218" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="219" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="220" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="221" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="222" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="223" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="224" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="225" ht="13.5" customHeight="1"/>
     <row r="226" ht="13.5" customHeight="1"/>
     <row r="227" ht="13.5" customHeight="1"/>
@@ -3300,6 +3370,11 @@
     <row r="1066" ht="13.5" customHeight="1"/>
     <row r="1067" ht="13.5" customHeight="1"/>
     <row r="1068" ht="13.5" customHeight="1"/>
+    <row r="1069" ht="13.5" customHeight="1"/>
+    <row r="1070" ht="13.5" customHeight="1"/>
+    <row r="1071" ht="13.5" customHeight="1"/>
+    <row r="1072" ht="13.5" customHeight="1"/>
+    <row r="1073" ht="13.5" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
